--- a/discord/wifey_swing_trades_2026-05-25.xlsx
+++ b/discord/wifey_swing_trades_2026-05-25.xlsx
@@ -679,21 +679,21 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>430C</t>
+          <t>640C</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>6.18</v>
+        <v>15.83</v>
       </c>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="5" t="n"/>
@@ -720,32 +720,32 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>EWY</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>2027-01-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>155C</t>
+          <t>430C</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>20</v>
+        <v>6.18</v>
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="6" t="n">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
@@ -761,32 +761,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>EWY</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2027-01-20</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>120C</t>
+          <t>155C</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.85</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="5" t="n"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="6" t="n">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
@@ -802,32 +802,32 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>500C</t>
+          <t>120C</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>15.5</v>
+        <v>7.85</v>
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="5" t="n"/>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="6" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
@@ -843,32 +843,32 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7900C</t>
+          <t>500C</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>3.55</v>
+        <v>15.5</v>
       </c>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="5" t="n"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>260C</t>
+          <t>7900C</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>23</v>
+        <v>3.55</v>
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="6" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
@@ -925,81 +925,77 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>150C</t>
+          <t>260C</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.315000000000001</v>
+        <v>23</v>
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="5" t="n"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="I11" s="3" t="n"/>
       <c r="J11" s="6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Open. 2 adds.</t>
+          <t>Open.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>250C</t>
+          <t>150C</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>13.7</v>
+        <v>9.315000000000001</v>
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="5" t="n"/>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="6" t="n">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open. 2 adds.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1007,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1021,21 +1017,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>450C</t>
+          <t>250C</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>-1</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
@@ -1044,11 +1036,11 @@
         </is>
       </c>
       <c r="J13" s="6" t="n">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Expired</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1060,44 +1052,44 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7900C</t>
+          <t>450C</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.55</v>
+        <v>6.5</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>3.19718309859155</v>
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired</t>
         </is>
       </c>
     </row>
@@ -1109,40 +1101,40 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>500C</t>
+          <t>7900C</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>15.5</v>
+        <v>3.55</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>100</v>
+        <v>14.9</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>5.451612903225806</v>
+        <v>3.19718309859155</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
@@ -1158,44 +1150,44 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>EWY</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>135C</t>
+          <t>500C</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>-1</v>
+        <v>100</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>5.451612903225806</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1199,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>EWY</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1217,11 +1209,11 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>45C</t>
+          <t>135C</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
@@ -1231,7 +1223,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1240,7 +1232,7 @@
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
@@ -1256,21 +1248,21 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>595C</t>
+          <t>45C</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>0</v>
@@ -1280,16 +1272,16 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
@@ -1305,21 +1297,21 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>300C</t>
+          <t>595C</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0</v>
@@ -1329,16 +1321,16 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
@@ -1354,7 +1346,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1364,11 +1356,11 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>400C</t>
+          <t>300C</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
@@ -1378,7 +1370,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1387,7 +1379,7 @@
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
@@ -1403,7 +1395,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1413,11 +1405,11 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>590C</t>
+          <t>400C</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>0</v>
@@ -1427,7 +1419,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
@@ -1436,7 +1428,7 @@
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
@@ -1452,7 +1444,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1462,11 +1454,11 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>270C</t>
+          <t>590C</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>8.475</v>
+        <v>12</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
@@ -1476,7 +1468,7 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -1485,7 +1477,7 @@
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
@@ -1501,7 +1493,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1511,11 +1503,11 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>55C</t>
+          <t>270C</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.15</v>
+        <v>8.475</v>
       </c>
       <c r="F23" s="4" t="n">
         <v>0</v>
@@ -1525,7 +1517,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
@@ -1534,7 +1526,7 @@
         </is>
       </c>
       <c r="J23" s="6" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
@@ -1550,7 +1542,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1560,11 +1552,11 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>450C</t>
+          <t>55C</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6</v>
+        <v>1.15</v>
       </c>
       <c r="F24" s="4" t="n">
         <v>0</v>
@@ -1574,7 +1566,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
@@ -1583,7 +1575,7 @@
         </is>
       </c>
       <c r="J24" s="6" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
@@ -1599,7 +1591,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>EWY</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1609,11 +1601,11 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>170C</t>
+          <t>450C</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>19.2</v>
+        <v>6</v>
       </c>
       <c r="F25" s="4" t="n">
         <v>0</v>
@@ -1623,7 +1615,7 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
@@ -1632,7 +1624,7 @@
         </is>
       </c>
       <c r="J25" s="6" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
@@ -1648,21 +1640,21 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>UAMY</t>
+          <t>EWY</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>12.5C</t>
+          <t>170C</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.75</v>
+        <v>19.2</v>
       </c>
       <c r="F26" s="4" t="n">
         <v>0</v>
@@ -1672,16 +1664,16 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
@@ -1697,44 +1689,44 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>EWY</t>
+          <t>UAMY</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>135C</t>
+          <t>12.5C</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>0.3902439024390246</v>
+        <v>0</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>7</v>
+        <v>122</v>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -1746,44 +1738,44 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>EWY</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>300C</t>
+          <t>135C</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10</v>
+        <v>4.1</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>3.25</v>
+        <v>5.7</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>0.3902439024390246</v>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (25% of peak)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -1795,40 +1787,44 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>640C</t>
+          <t>300C</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="5" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>3.25</v>
+      </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
           <t>2026-01-29</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
       <c r="J29" s="6" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>Rolled</t>
+          <t>Scale out 1/2 (25% of peak)</t>
         </is>
       </c>
     </row>
@@ -5756,40 +5752,44 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>230C</t>
+          <t>210C</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F110" s="4" t="n"/>
-      <c r="G110" s="5" t="n"/>
+        <v>3.65</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="G110" s="9" t="n">
+        <v>0.8767123287671232</v>
+      </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="J110" s="6" t="n">
-        <v>904</v>
+        <v>20</v>
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>Rolled</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -5801,44 +5801,44 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>210C</t>
+          <t>28C</t>
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>3.65</v>
+        <v>256</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="G111" s="9" t="n">
-        <v>0.8767123287671232</v>
+        <v>0</v>
+      </c>
+      <c r="G111" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="J111" s="6" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -5860,11 +5860,11 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>28C</t>
+          <t>100C</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
       <c r="F112" s="4" t="n">
         <v>0</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="J112" s="6" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -5909,11 +5909,11 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>70C</t>
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F113" s="4" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="J113" s="6" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="K113" s="3" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -5958,11 +5958,11 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>70C</t>
+          <t>250C</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="F114" s="4" t="n">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="J114" s="6" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
@@ -6014,10 +6014,10 @@
         <v>3.65</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" s="8" t="n">
-        <v>-1</v>
+        <v>-0.726027397260274</v>
       </c>
       <c r="H115" s="3" t="inlineStr">
         <is>
@@ -6026,15 +6026,15 @@
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="J115" s="6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -6046,40 +6046,40 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>250C</t>
+          <t>180C</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
-        <v>3.65</v>
+        <v>14.63333333333333</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="8" t="n">
-        <v>-0.726027397260274</v>
+        <v>14</v>
+      </c>
+      <c r="G116" s="11" t="n">
+        <v>-0.04328018223234621</v>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="J116" s="6" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
@@ -6095,40 +6095,40 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>180C</t>
+          <t>230P</t>
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>14.63333333333333</v>
+        <v>7.4</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G117" s="11" t="n">
-        <v>-0.04328018223234621</v>
+        <v>-0.4594594594594595</v>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="J117" s="6" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
@@ -6144,27 +6144,27 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>230P</t>
+          <t>70C</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G118" s="11" t="n">
-        <v>-0.4594594594594595</v>
+        <v>6</v>
+      </c>
+      <c r="G118" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
@@ -6193,44 +6193,44 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>70C</t>
+          <t>420C</t>
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>3</v>
+        <v>13.8</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G119" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H119" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="J119" s="6" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -6252,11 +6252,11 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>420C</t>
+          <t>330C</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>13.8</v>
+        <v>5.53</v>
       </c>
       <c r="F120" s="4" t="n">
         <v>0</v>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="H120" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="J120" s="6" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -6301,11 +6301,11 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>330C</t>
+          <t>200P</t>
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>5.53</v>
+        <v>2.67</v>
       </c>
       <c r="F121" s="4" t="n">
         <v>0</v>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="H121" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="J121" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K121" s="3" t="inlineStr">
         <is>
@@ -6350,11 +6350,11 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>200P</t>
+          <t>222C</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>2.67</v>
+        <v>2.175</v>
       </c>
       <c r="F122" s="4" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="J122" s="6" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -6399,11 +6399,11 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>222C</t>
+          <t>285C</t>
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>2.175</v>
+        <v>4.85</v>
       </c>
       <c r="F123" s="4" t="n">
         <v>0</v>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="H123" s="3" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="J123" s="6" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K123" s="3" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IBIT</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -6448,34 +6448,34 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>285C</t>
+          <t>65C</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
-        <v>4.85</v>
+        <v>2.13</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="8" t="n">
-        <v>-1</v>
+        <v>4.6</v>
+      </c>
+      <c r="G124" s="9" t="n">
+        <v>1.15962441314554</v>
       </c>
       <c r="H124" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="J124" s="6" t="n">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Rolled</t>
         </is>
       </c>
     </row>
@@ -6487,44 +6487,44 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>IBIT</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>65C</t>
+          <t>450C</t>
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>2.13</v>
+        <v>2.72</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G125" s="9" t="n">
-        <v>1.15962441314554</v>
+        <v>0</v>
+      </c>
+      <c r="G125" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="J125" s="6" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t>Rolled</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -6546,11 +6546,11 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>450C</t>
+          <t>1400C</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="F126" s="4" t="n">
         <v>0</v>
@@ -6585,44 +6585,44 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>1400C</t>
+          <t>100C</t>
         </is>
       </c>
       <c r="E127" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F127" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" s="8" t="n">
-        <v>-1</v>
+      <c r="G127" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="J127" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K127" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -6634,44 +6634,44 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>TQQQ</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>80C</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="J128" s="6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Rolled</t>
         </is>
       </c>
     </row>
@@ -6683,44 +6683,44 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>TQQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>80C</t>
+          <t>520P</t>
         </is>
       </c>
       <c r="E129" s="4" t="n">
-        <v>2.8</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="G129" s="9" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
+      </c>
+      <c r="G129" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="J129" s="6" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="K129" s="3" t="inlineStr">
         <is>
-          <t>Rolled</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -6742,11 +6742,11 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>520P</t>
+          <t>130C</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>8.710000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="F130" s="4" t="n">
         <v>0</v>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -6791,11 +6791,11 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>130C</t>
+          <t>50C</t>
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="F131" s="4" t="n">
         <v>0</v>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="J131" s="6" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="K131" s="3" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -6840,11 +6840,11 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>50C</t>
+          <t>167.5C</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>3.68</v>
+        <v>4.98</v>
       </c>
       <c r="F132" s="4" t="n">
         <v>0</v>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -6863,7 +6863,7 @@
         </is>
       </c>
       <c r="J132" s="6" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -6889,11 +6889,11 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>167.5C</t>
+          <t>310C</t>
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>4.98</v>
+        <v>4.5</v>
       </c>
       <c r="F133" s="4" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="J133" s="6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -6938,11 +6938,11 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>310C</t>
+          <t>100C</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="F134" s="4" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="H134" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="J134" s="6" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -6987,34 +6987,34 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>100C</t>
+          <t>310C</t>
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>1.4</v>
+        <v>4.5</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" s="8" t="n">
-        <v>-1</v>
+        <v>7.3</v>
+      </c>
+      <c r="G135" s="9" t="n">
+        <v>0.6222222222222222</v>
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="J135" s="6" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -7036,26 +7036,26 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>310C</t>
+          <t>167.5C</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>4.5</v>
+        <v>4.98</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>7.3</v>
+        <v>11.5</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>0.6222222222222222</v>
+        <v>1.309236947791165</v>
       </c>
       <c r="H136" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="J136" s="6" t="n">
@@ -7075,40 +7075,40 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>167.5C</t>
+          <t>420C</t>
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>4.98</v>
+        <v>13.8</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G137" s="9" t="n">
-        <v>1.309236947791165</v>
+        <v>10.5</v>
+      </c>
+      <c r="G137" s="11" t="n">
+        <v>-0.2391304347826088</v>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="J137" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K137" s="3" t="inlineStr">
         <is>
@@ -7124,44 +7124,44 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>420C</t>
+          <t>176P</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>13.8</v>
+        <v>3.25</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G138" s="11" t="n">
-        <v>-0.2391304347826088</v>
+        <v>0</v>
+      </c>
+      <c r="G138" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="J138" s="6" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>IBIT</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -7183,11 +7183,11 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>176P</t>
+          <t>50C</t>
         </is>
       </c>
       <c r="E139" s="4" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="F139" s="4" t="n">
         <v>0</v>
@@ -7232,11 +7232,11 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>50C</t>
+          <t>55C</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="F140" s="4" t="n">
         <v>0</v>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="J140" s="6" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
@@ -7281,11 +7281,11 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>55C</t>
+          <t>60C</t>
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>1.67</v>
+        <v>1.94</v>
       </c>
       <c r="F141" s="4" t="n">
         <v>0</v>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="H141" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="J141" s="6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K141" s="3" t="inlineStr">
         <is>
@@ -7320,36 +7320,36 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>IBIT</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>60C</t>
+          <t>130C</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" s="8" t="n">
-        <v>-1</v>
+        <v>9</v>
+      </c>
+      <c r="G142" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="H142" s="3" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="J142" s="6" t="n">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -7369,44 +7369,44 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>130C</t>
+          <t>520C</t>
         </is>
       </c>
       <c r="E143" s="4" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G143" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="J143" s="6" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -7418,21 +7418,21 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>520C</t>
+          <t>615C</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="F144" s="4" t="n">
         <v>0</v>
@@ -7442,16 +7442,16 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="J144" s="6" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
@@ -7467,7 +7467,7 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>DIA</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -7477,11 +7477,11 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>615C</t>
+          <t>440C</t>
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="F145" s="4" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -7500,7 +7500,7 @@
         </is>
       </c>
       <c r="J145" s="6" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K145" s="3" t="inlineStr">
         <is>
@@ -7516,21 +7516,21 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>DIA</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>440C</t>
+          <t>240C</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="F146" s="4" t="n">
         <v>0</v>
@@ -7540,16 +7540,16 @@
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="J146" s="6" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -7575,11 +7575,11 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>240C</t>
+          <t>519C</t>
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>2.67</v>
+        <v>4.6</v>
       </c>
       <c r="F147" s="4" t="n">
         <v>0</v>
@@ -7614,21 +7614,21 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>519C</t>
+          <t>300C</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>4.6</v>
+        <v>3.63</v>
       </c>
       <c r="F148" s="4" t="n">
         <v>0</v>
@@ -7638,16 +7638,16 @@
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>2024-11-08</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="J148" s="6" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -7673,11 +7673,11 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>300C</t>
+          <t>585C</t>
         </is>
       </c>
       <c r="E149" s="4" t="n">
-        <v>3.63</v>
+        <v>3.9</v>
       </c>
       <c r="F149" s="4" t="n">
         <v>0</v>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="J149" s="6" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="K149" s="3" t="inlineStr">
         <is>
@@ -7717,16 +7717,16 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>585C</t>
+          <t>590C</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
-        <v>3.9</v>
+        <v>0.38</v>
       </c>
       <c r="F150" s="4" t="n">
         <v>0</v>
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="J150" s="6" t="n">
@@ -7761,21 +7761,21 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>590C</t>
+          <t>490C</t>
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>0.38</v>
+        <v>7.87</v>
       </c>
       <c r="F151" s="4" t="n">
         <v>0</v>
@@ -7785,16 +7785,16 @@
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="J151" s="6" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="K151" s="3" t="inlineStr">
         <is>
@@ -7810,21 +7810,21 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>490C</t>
+          <t>228C</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>7.87</v>
+        <v>2.1</v>
       </c>
       <c r="F152" s="4" t="n">
         <v>0</v>
@@ -7834,16 +7834,16 @@
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="J152" s="6" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
@@ -7864,16 +7864,16 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>228C</t>
+          <t>205C</t>
         </is>
       </c>
       <c r="E153" s="4" t="n">
-        <v>2.1</v>
+        <v>5.75</v>
       </c>
       <c r="F153" s="4" t="n">
         <v>0</v>
@@ -7883,16 +7883,16 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="J153" s="6" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
@@ -7908,21 +7908,21 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>205C</t>
+          <t>145C</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
-        <v>5.75</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F154" s="4" t="n">
         <v>0</v>
@@ -7932,16 +7932,16 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="J154" s="6" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
@@ -7957,21 +7957,21 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>145C</t>
+          <t>920C</t>
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>9.300000000000001</v>
+        <v>21</v>
       </c>
       <c r="F155" s="4" t="n">
         <v>0</v>
@@ -7981,16 +7981,16 @@
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>2024-06-21</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="J155" s="6" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="K155" s="3" t="inlineStr">
         <is>
@@ -8006,21 +8006,21 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>920C</t>
+          <t>430C</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
-        <v>21</v>
+        <v>5.73</v>
       </c>
       <c r="F156" s="4" t="n">
         <v>0</v>
@@ -8030,16 +8030,16 @@
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-04-19</t>
         </is>
       </c>
       <c r="J156" s="6" t="n">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
@@ -8055,21 +8055,21 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>430C</t>
+          <t>205C</t>
         </is>
       </c>
       <c r="E157" s="4" t="n">
-        <v>5.73</v>
+        <v>2.88</v>
       </c>
       <c r="F157" s="4" t="n">
         <v>0</v>
@@ -8079,16 +8079,16 @@
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2024-01-03</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>2024-04-19</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="J157" s="6" t="n">
-        <v>126</v>
+        <v>44</v>
       </c>
       <c r="K157" s="3" t="inlineStr">
         <is>
@@ -8104,21 +8104,21 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>205C</t>
+          <t>25C</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
-        <v>2.88</v>
+        <v>2.33</v>
       </c>
       <c r="F158" s="4" t="n">
         <v>0</v>
@@ -8128,16 +8128,16 @@
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>2024-01-03</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>2024-02-16</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="J158" s="6" t="n">
-        <v>44</v>
+        <v>172</v>
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
@@ -8153,40 +8153,44 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>2023-10-06</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>436C</t>
+          <t>150C</t>
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F159" s="4" t="n"/>
-      <c r="G159" s="5" t="n"/>
+        <v>4.75</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" s="8" t="n">
+        <v>-1</v>
+      </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2023-08-30</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="J159" s="6" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="K159" s="3" t="inlineStr">
         <is>
-          <t>Rolled</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -8198,21 +8202,21 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>25C</t>
+          <t>1980C</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
-        <v>2.33</v>
+        <v>10.8</v>
       </c>
       <c r="F160" s="4" t="n">
         <v>0</v>
@@ -8222,16 +8226,16 @@
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="J160" s="6" t="n">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
@@ -8247,21 +8251,21 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>150C</t>
+          <t>180C</t>
         </is>
       </c>
       <c r="E161" s="4" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="F161" s="4" t="n">
         <v>0</v>
@@ -8271,16 +8275,16 @@
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>2023-08-30</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>2024-01-19</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="J161" s="6" t="n">
-        <v>142</v>
+        <v>25</v>
       </c>
       <c r="K161" s="3" t="inlineStr">
         <is>
@@ -8296,21 +8300,21 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>1980C</t>
+          <t>383P</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>10.8</v>
+        <v>0.87</v>
       </c>
       <c r="F162" s="4" t="n">
         <v>0</v>
@@ -8320,16 +8324,16 @@
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="J162" s="6" t="n">
-        <v>127</v>
+        <v>336</v>
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
@@ -8345,21 +8349,21 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>180C</t>
+          <t>150C</t>
         </is>
       </c>
       <c r="E163" s="4" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="F163" s="4" t="n">
         <v>0</v>
@@ -8369,16 +8373,16 @@
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="J163" s="6" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="K163" s="3" t="inlineStr">
         <is>
@@ -8394,21 +8398,21 @@
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>383P</t>
+          <t>39C</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
-        <v>0.87</v>
+        <v>1.15</v>
       </c>
       <c r="F164" s="4" t="n">
         <v>0</v>
@@ -8418,16 +8422,16 @@
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="J164" s="6" t="n">
-        <v>336</v>
+        <v>35</v>
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
@@ -8443,7 +8447,7 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -8453,11 +8457,11 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>150C</t>
+          <t>190C</t>
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>2.3</v>
+        <v>0.98</v>
       </c>
       <c r="F165" s="4" t="n">
         <v>0</v>
@@ -8467,7 +8471,7 @@
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
@@ -8476,7 +8480,7 @@
         </is>
       </c>
       <c r="J165" s="6" t="n">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="K165" s="3" t="inlineStr">
         <is>
@@ -8492,7 +8496,7 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -8502,11 +8506,11 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>39C</t>
+          <t>336P</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>1.15</v>
+        <v>4.37</v>
       </c>
       <c r="F166" s="4" t="n">
         <v>0</v>
@@ -8516,7 +8520,7 @@
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="I166" s="3" t="inlineStr">
@@ -8525,7 +8529,7 @@
         </is>
       </c>
       <c r="J166" s="6" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
@@ -8541,7 +8545,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -8551,11 +8555,11 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>190C</t>
+          <t>320C</t>
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>0.98</v>
+        <v>4</v>
       </c>
       <c r="F167" s="4" t="n">
         <v>0</v>
@@ -8565,7 +8569,7 @@
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="I167" s="3" t="inlineStr">
@@ -8574,7 +8578,7 @@
         </is>
       </c>
       <c r="J167" s="6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K167" s="3" t="inlineStr">
         <is>
@@ -8590,21 +8594,21 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SMH</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-10-27</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>336P</t>
+          <t>150C</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>4.37</v>
+        <v>3</v>
       </c>
       <c r="F168" s="4" t="n">
         <v>0</v>
@@ -8614,16 +8618,16 @@
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
           <t>2023-10-27</t>
         </is>
       </c>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>2023-11-17</t>
-        </is>
-      </c>
       <c r="J168" s="6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
@@ -8639,21 +8643,21 @@
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>320C</t>
+          <t>30C</t>
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F169" s="4" t="n">
         <v>0</v>
@@ -8663,16 +8667,16 @@
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="J169" s="6" t="n">
-        <v>15</v>
+        <v>218</v>
       </c>
       <c r="K169" s="3" t="inlineStr">
         <is>
@@ -8688,21 +8692,21 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>150C</t>
+          <t>125C</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F170" s="4" t="n">
         <v>0</v>
@@ -8712,16 +8716,16 @@
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>2023-10-27</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="J170" s="6" t="n">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
@@ -8737,7 +8741,7 @@
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -8747,11 +8751,11 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>30C</t>
+          <t>143C</t>
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="F171" s="4" t="n">
         <v>0</v>
@@ -8761,7 +8765,7 @@
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>2023-03-16</t>
+          <t>2023-10-04</t>
         </is>
       </c>
       <c r="I171" s="3" t="inlineStr">
@@ -8770,7 +8774,7 @@
         </is>
       </c>
       <c r="J171" s="6" t="n">
-        <v>218</v>
+        <v>16</v>
       </c>
       <c r="K171" s="3" t="inlineStr">
         <is>
@@ -8786,44 +8790,44 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>CCJ</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-11-17</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>143C</t>
+          <t>39C</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
-        <v>3.45</v>
+        <v>1.15</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" s="8" t="n">
-        <v>-1</v>
+        <v>1.7</v>
+      </c>
+      <c r="G172" s="10" t="n">
+        <v>0.4782608695652175</v>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>2023-10-04</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="J172" s="6" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -8835,44 +8839,44 @@
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>CCJ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>2023-11-17</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>39C</t>
+          <t>440C</t>
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>1.15</v>
+        <v>2.44</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G173" s="10" t="n">
-        <v>0.4782608695652175</v>
+        <v>0</v>
+      </c>
+      <c r="G173" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H173" s="3" t="inlineStr">
         <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
           <t>2023-10-13</t>
         </is>
       </c>
-      <c r="I173" s="3" t="inlineStr">
-        <is>
-          <t>2023-10-17</t>
-        </is>
-      </c>
       <c r="J173" s="6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K173" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -8884,44 +8888,40 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-03-17</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>440C</t>
+          <t>195C</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="F174" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" s="8" t="n">
-        <v>-1</v>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="F174" s="4" t="n"/>
+      <c r="G174" s="5" t="n"/>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>2023-09-25</t>
+          <t>2023-03-14</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="J174" s="6" t="n">
-        <v>18</v>
+        <v>210</v>
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -8933,40 +8933,44 @@
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
         <is>
-          <t>2023-03-17</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>195C</t>
+          <t>181.5C</t>
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="F175" s="4" t="n"/>
-      <c r="G175" s="5" t="n"/>
+        <v>0.93</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" s="8" t="n">
+        <v>-1</v>
+      </c>
       <c r="H175" s="3" t="inlineStr">
         <is>
-          <t>2023-03-14</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="I175" s="3" t="inlineStr">
         <is>
-          <t>2023-10-10</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="J175" s="6" t="n">
-        <v>210</v>
+        <v>17</v>
       </c>
       <c r="K175" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -8978,7 +8982,7 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -8988,11 +8992,11 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>181.5C</t>
+          <t>436C</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>0.93</v>
+        <v>1.19</v>
       </c>
       <c r="F176" s="4" t="n">
         <v>0</v>
@@ -9002,7 +9006,7 @@
       </c>
       <c r="H176" s="3" t="inlineStr">
         <is>
-          <t>2023-09-19</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="I176" s="3" t="inlineStr">
@@ -9011,7 +9015,7 @@
         </is>
       </c>
       <c r="J176" s="6" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
@@ -9611,40 +9615,44 @@
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>125C</t>
+          <t>110C</t>
         </is>
       </c>
       <c r="E189" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F189" s="4" t="n"/>
-      <c r="G189" s="5" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="F189" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" s="8" t="n">
+        <v>-1</v>
+      </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="J189" s="6" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="K189" s="3" t="inlineStr">
         <is>
-          <t>Rolled</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -9656,7 +9664,7 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -9666,11 +9674,11 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>110C</t>
+          <t>65C</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="F190" s="4" t="n">
         <v>0</v>
@@ -9680,7 +9688,7 @@
       </c>
       <c r="H190" s="3" t="inlineStr">
         <is>
-          <t>2023-06-05</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="I190" s="3" t="inlineStr">
@@ -9689,7 +9697,7 @@
         </is>
       </c>
       <c r="J190" s="6" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
@@ -9705,7 +9713,7 @@
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -9715,11 +9723,11 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>65C</t>
+          <t>300C</t>
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>2.34</v>
+        <v>6.6</v>
       </c>
       <c r="F191" s="4" t="n">
         <v>0</v>
@@ -9729,7 +9737,7 @@
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>2023-06-12</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -9738,7 +9746,7 @@
         </is>
       </c>
       <c r="J191" s="6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K191" s="3" t="inlineStr">
         <is>
@@ -9754,21 +9762,21 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>300C</t>
+          <t>110C</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
-        <v>6.6</v>
+        <v>2.15</v>
       </c>
       <c r="F192" s="4" t="n">
         <v>0</v>
@@ -9778,16 +9786,16 @@
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="J192" s="6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
@@ -9803,7 +9811,7 @@
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -9813,11 +9821,11 @@
       </c>
       <c r="D193" s="3" t="inlineStr">
         <is>
-          <t>110C</t>
+          <t>128C</t>
         </is>
       </c>
       <c r="E193" s="4" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="F193" s="4" t="n">
         <v>0</v>
@@ -9827,7 +9835,7 @@
       </c>
       <c r="H193" s="3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="I193" s="3" t="inlineStr">
@@ -9836,7 +9844,7 @@
         </is>
       </c>
       <c r="J193" s="6" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K193" s="3" t="inlineStr">
         <is>
@@ -9852,7 +9860,7 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -9862,34 +9870,34 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>128C</t>
+          <t>110C</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" s="8" t="n">
-        <v>-1</v>
+        <v>17</v>
+      </c>
+      <c r="G194" s="9" t="n">
+        <v>6.906976744186046</v>
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>2023-06-07</t>
+          <t>2023-05-10</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-05-26</t>
         </is>
       </c>
       <c r="J194" s="6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -9901,12 +9909,12 @@
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="D195" s="3" t="inlineStr">
@@ -9915,30 +9923,30 @@
         </is>
       </c>
       <c r="E195" s="4" t="n">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="G195" s="9" t="n">
-        <v>6.906976744186046</v>
+        <v>0</v>
+      </c>
+      <c r="G195" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2023-04-10</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
         <is>
-          <t>2023-05-26</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="J195" s="6" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="K195" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9958,7 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>TLT</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -9960,11 +9968,11 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>110C</t>
+          <t>160C</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>1.54</v>
+        <v>3.33</v>
       </c>
       <c r="F196" s="4" t="n">
         <v>0</v>
@@ -9974,7 +9982,7 @@
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>2023-04-10</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
@@ -9983,7 +9991,7 @@
         </is>
       </c>
       <c r="J196" s="6" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
@@ -9999,7 +10007,7 @@
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ZION</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -10009,11 +10017,11 @@
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>160C</t>
+          <t>15P</t>
         </is>
       </c>
       <c r="E197" s="4" t="n">
-        <v>3.33</v>
+        <v>1.3</v>
       </c>
       <c r="F197" s="4" t="n">
         <v>0</v>
@@ -10023,7 +10031,7 @@
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
@@ -10032,7 +10040,7 @@
         </is>
       </c>
       <c r="J197" s="6" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K197" s="3" t="inlineStr">
         <is>
@@ -10048,21 +10056,21 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>ZION</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>15P</t>
+          <t>290C</t>
         </is>
       </c>
       <c r="E198" s="4" t="n">
-        <v>1.3</v>
+        <v>1.93</v>
       </c>
       <c r="F198" s="4" t="n">
         <v>0</v>
@@ -10077,11 +10085,11 @@
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
+          <t>2023-05-12</t>
         </is>
       </c>
       <c r="J198" s="6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
@@ -10097,7 +10105,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -10107,11 +10115,11 @@
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>290C</t>
+          <t>92C</t>
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>1.93</v>
+        <v>1</v>
       </c>
       <c r="F199" s="4" t="n">
         <v>0</v>
@@ -10146,21 +10154,21 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>92C</t>
+          <t>280C</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
-        <v>1</v>
+        <v>3.55</v>
       </c>
       <c r="F200" s="4" t="n">
         <v>0</v>
@@ -10170,16 +10178,16 @@
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>2023-05-04</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="J200" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
@@ -10212,10 +10220,10 @@
         <v>3.55</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" s="8" t="n">
-        <v>-1</v>
+        <v>9</v>
+      </c>
+      <c r="G201" s="9" t="n">
+        <v>1.535211267605634</v>
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
@@ -10224,15 +10232,15 @@
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="J201" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10289,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Scale out 1/2 (25% of peak)</t>
         </is>
       </c>
     </row>
@@ -10293,44 +10301,44 @@
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>280C</t>
+          <t>110C</t>
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>3.55</v>
+        <v>1.4</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G203" s="9" t="n">
-        <v>1.535211267605634</v>
+        <v>0</v>
+      </c>
+      <c r="G203" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H203" s="3" t="inlineStr">
         <is>
+          <t>2023-04-04</t>
+        </is>
+      </c>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
           <t>2023-04-28</t>
         </is>
       </c>
-      <c r="I203" s="3" t="inlineStr">
-        <is>
-          <t>2023-05-01</t>
-        </is>
-      </c>
       <c r="J203" s="6" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="K203" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (25% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10350,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -10352,11 +10360,11 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>110C</t>
+          <t>305C</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="F204" s="4" t="n">
         <v>0</v>
@@ -10366,7 +10374,7 @@
       </c>
       <c r="H204" s="3" t="inlineStr">
         <is>
-          <t>2023-04-04</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="I204" s="3" t="inlineStr">
@@ -10375,7 +10383,7 @@
         </is>
       </c>
       <c r="J204" s="6" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
@@ -10391,44 +10399,44 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>305C</t>
+          <t>390P</t>
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" s="8" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="G205" s="11" t="n">
+        <v>-0.2857142857142856</v>
       </c>
       <c r="H205" s="3" t="inlineStr">
         <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
           <t>2023-04-27</t>
         </is>
       </c>
-      <c r="I205" s="3" t="inlineStr">
-        <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
       <c r="J205" s="6" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K205" s="3" t="inlineStr">
         <is>
-          <t>Expired (no explicit close; assumed worthless)</t>
+          <t>Scale out 1/2 (50% of peak)</t>
         </is>
       </c>
     </row>
@@ -10440,44 +10448,44 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>2023-03-24</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>390P</t>
+          <t>230C</t>
         </is>
       </c>
       <c r="E206" s="4" t="n">
-        <v>1.4</v>
+        <v>7.5</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" s="11" t="n">
-        <v>-0.2857142857142856</v>
+        <v>0</v>
+      </c>
+      <c r="G206" s="8" t="n">
+        <v>-1</v>
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>2023-03-22</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2023-04-21</t>
         </is>
       </c>
       <c r="J206" s="6" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>Scale out 1/2 (50% of peak)</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18260,7 @@
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C366" s="3" t="inlineStr">
@@ -18262,11 +18270,11 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>81C</t>
+          <t>950C</t>
         </is>
       </c>
       <c r="E366" s="4" t="n">
-        <v>2.95</v>
+        <v>6.2</v>
       </c>
       <c r="F366" s="4" t="n">
         <v>0</v>
@@ -18276,7 +18284,7 @@
       </c>
       <c r="H366" s="3" t="inlineStr">
         <is>
-          <t>2022-08-11</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="I366" s="3" t="inlineStr">
@@ -18285,7 +18293,7 @@
         </is>
       </c>
       <c r="J366" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
@@ -18301,7 +18309,7 @@
       </c>
       <c r="B367" s="3" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="C367" s="3" t="inlineStr">
@@ -18311,11 +18319,11 @@
       </c>
       <c r="D367" s="3" t="inlineStr">
         <is>
-          <t>172.5C</t>
+          <t>81C</t>
         </is>
       </c>
       <c r="E367" s="4" t="n">
-        <v>2.35</v>
+        <v>2.95</v>
       </c>
       <c r="F367" s="4" t="n">
         <v>0</v>
@@ -18325,7 +18333,7 @@
       </c>
       <c r="H367" s="3" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2022-08-11</t>
         </is>
       </c>
       <c r="I367" s="3" t="inlineStr">
@@ -18334,7 +18342,7 @@
         </is>
       </c>
       <c r="J367" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K367" s="3" t="inlineStr">
         <is>
@@ -18350,7 +18358,7 @@
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C368" s="3" t="inlineStr">
@@ -18360,30 +18368,34 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>950C</t>
+          <t>172.5C</t>
         </is>
       </c>
       <c r="E368" s="4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F368" s="4" t="n"/>
-      <c r="G368" s="5" t="n"/>
+        <v>2.35</v>
+      </c>
+      <c r="F368" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" s="8" t="n">
+        <v>-1</v>
+      </c>
       <c r="H368" s="3" t="inlineStr">
         <is>
-          <t>2022-08-10</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="I368" s="3" t="inlineStr">
         <is>
-          <t>2022-08-15</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="J368" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>Rolled</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
@@ -18787,7 +18799,7 @@
       </c>
       <c r="B377" s="3" t="inlineStr">
         <is>
-          <t>ETSY</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C377" s="3" t="inlineStr">
@@ -18797,11 +18809,11 @@
       </c>
       <c r="D377" s="3" t="inlineStr">
         <is>
-          <t>80P</t>
+          <t>155C</t>
         </is>
       </c>
       <c r="E377" s="4" t="n">
-        <v>2.7</v>
+        <v>1.06</v>
       </c>
       <c r="F377" s="4" t="n">
         <v>0</v>
@@ -18811,7 +18823,7 @@
       </c>
       <c r="H377" s="3" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="I377" s="3" t="inlineStr">
@@ -18820,7 +18832,7 @@
         </is>
       </c>
       <c r="J377" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K377" s="3" t="inlineStr">
         <is>
@@ -18836,7 +18848,7 @@
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>VIX</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="C378" s="3" t="inlineStr">
@@ -18846,11 +18858,11 @@
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>150C</t>
+          <t>80P</t>
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>2.11</v>
+        <v>2.7</v>
       </c>
       <c r="F378" s="4" t="n">
         <v>0</v>
@@ -18860,7 +18872,7 @@
       </c>
       <c r="H378" s="3" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="I378" s="3" t="inlineStr">
@@ -18869,7 +18881,7 @@
         </is>
       </c>
       <c r="J378" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
@@ -18885,7 +18897,7 @@
       </c>
       <c r="B379" s="3" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>VIX</t>
         </is>
       </c>
       <c r="C379" s="3" t="inlineStr">
@@ -18895,11 +18907,11 @@
       </c>
       <c r="D379" s="3" t="inlineStr">
         <is>
-          <t>114C</t>
+          <t>150C</t>
         </is>
       </c>
       <c r="E379" s="4" t="n">
-        <v>1.15</v>
+        <v>2.11</v>
       </c>
       <c r="F379" s="4" t="n">
         <v>0</v>
@@ -18909,7 +18921,7 @@
       </c>
       <c r="H379" s="3" t="inlineStr">
         <is>
-          <t>2022-07-18</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="I379" s="3" t="inlineStr">
@@ -18918,7 +18930,7 @@
         </is>
       </c>
       <c r="J379" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K379" s="3" t="inlineStr">
         <is>
@@ -18934,7 +18946,7 @@
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>SNAP</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C380" s="3" t="inlineStr">
@@ -18944,11 +18956,11 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>15C</t>
+          <t>114C</t>
         </is>
       </c>
       <c r="E380" s="4" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="F380" s="4" t="n">
         <v>0</v>
@@ -18958,7 +18970,7 @@
       </c>
       <c r="H380" s="3" t="inlineStr">
         <is>
-          <t>2022-07-19</t>
+          <t>2022-07-18</t>
         </is>
       </c>
       <c r="I380" s="3" t="inlineStr">
@@ -18967,7 +18979,7 @@
         </is>
       </c>
       <c r="J380" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
@@ -18983,7 +18995,7 @@
       </c>
       <c r="B381" s="3" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SNAP</t>
         </is>
       </c>
       <c r="C381" s="3" t="inlineStr">
@@ -18993,11 +19005,11 @@
       </c>
       <c r="D381" s="3" t="inlineStr">
         <is>
-          <t>830C</t>
+          <t>15C</t>
         </is>
       </c>
       <c r="E381" s="4" t="n">
-        <v>8.25</v>
+        <v>1</v>
       </c>
       <c r="F381" s="4" t="n">
         <v>0</v>
@@ -19007,7 +19019,7 @@
       </c>
       <c r="H381" s="3" t="inlineStr">
         <is>
-          <t>2022-07-21</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="I381" s="3" t="inlineStr">
@@ -19016,7 +19028,7 @@
         </is>
       </c>
       <c r="J381" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K381" s="3" t="inlineStr">
         <is>
@@ -19032,21 +19044,21 @@
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="C382" s="3" t="inlineStr">
         <is>
-          <t>2022-07-20</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>374P</t>
+          <t>830C</t>
         </is>
       </c>
       <c r="E382" s="4" t="n">
-        <v>3</v>
+        <v>8.25</v>
       </c>
       <c r="F382" s="4" t="n">
         <v>0</v>
@@ -19056,16 +19068,16 @@
       </c>
       <c r="H382" s="3" t="inlineStr">
         <is>
-          <t>2022-07-14</t>
+          <t>2022-07-21</t>
         </is>
       </c>
       <c r="I382" s="3" t="inlineStr">
         <is>
-          <t>2022-07-20</t>
+          <t>2022-07-22</t>
         </is>
       </c>
       <c r="J382" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
@@ -19081,40 +19093,44 @@
       </c>
       <c r="B383" s="3" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="D383" s="3" t="inlineStr">
         <is>
-          <t>155C</t>
+          <t>374P</t>
         </is>
       </c>
       <c r="E383" s="4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="F383" s="4" t="n"/>
-      <c r="G383" s="5" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F383" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" s="8" t="n">
+        <v>-1</v>
+      </c>
       <c r="H383" s="3" t="inlineStr">
         <is>
-          <t>2022-07-13</t>
+          <t>2022-07-14</t>
         </is>
       </c>
       <c r="I383" s="3" t="inlineStr">
         <is>
-          <t>2022-07-18</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="J383" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K383" s="3" t="inlineStr">
         <is>
-          <t>Rolled</t>
+          <t>Expired (no explicit close; assumed worthless)</t>
         </is>
       </c>
     </row>
